--- a/ig/ch-elm/StructureDefinition-ch-elm-ext-vct-code.xlsx
+++ b/ig/ch-elm/StructureDefinition-ch-elm-ext-vct-code.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.13.1</t>
+    <t>1.14.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>retired</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-21T11:21:00+00:00</t>
+    <t>2026-05-26T14:58:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This CH ELM extension enables to provide the VCT Code.</t>
+    <t>This CH ELM extension enables to provide the VCT Code. Retired. Ues identifier instead (see Guidance)</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/ig/ch-elm/StructureDefinition-ch-elm-ext-vct-code.xlsx
+++ b/ig/ch-elm/StructureDefinition-ch-elm-ext-vct-code.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.14.0</t>
+    <t>1.14.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T14:58:40+00:00</t>
+    <t>2026-07-01T19:23:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/ch-elm/StructureDefinition-ch-elm-ext-vct-code.xlsx
+++ b/ig/ch-elm/StructureDefinition-ch-elm-ext-vct-code.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.14.1</t>
+    <t>1.15.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T19:23:08+00:00</t>
+    <t>2026-08-12T07:20:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/ch-elm/StructureDefinition-ch-elm-ext-vct-code.xlsx
+++ b/ig/ch-elm/StructureDefinition-ch-elm-ext-vct-code.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.15.0</t>
+    <t>1.15.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-12T07:20:00+00:00</t>
+    <t>2026-08-14T07:34:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -343,7 +343,7 @@
     <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
   </si>
   <si>
-    <t>20</t>
+    <t>100</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
